--- a/(枠)◯年度一式/管理月報/実施要領報告様式有価.xlsx
+++ b/(枠)◯年度一式/管理月報/実施要領報告様式有価.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\管理月報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8B0D8E-97A9-4340-A4E7-88EF682D1893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90114859-F5D6-4323-8A4D-ECD4055FCECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="315" windowWidth="15750" windowHeight="15480" xr2:uid="{57CE4AD5-2BC3-4110-8DAF-C104A3A5DEF1}"/>
+    <workbookView xWindow="3000" yWindow="45" windowWidth="20535" windowHeight="15480" xr2:uid="{57CE4AD5-2BC3-4110-8DAF-C104A3A5DEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="別記様式４" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">別記様式４!$A$1:$O$45</definedName>
@@ -921,6 +920,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -933,15 +962,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -960,12 +980,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -985,21 +999,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1022,6 +1021,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="A-1"/>
       <sheetName val="A-2"/>
@@ -1037,7 +1039,13 @@
       <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
@@ -1310,28 +1318,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="11"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>8</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2228,142 +2214,142 @@
       <c r="A1"/>
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="str">
-        <f>"令和"&amp;[13]Sheet1!$C$2&amp;"年度　破砕処理施設維持管理状況報告書"</f>
-        <v>令和8年度　破砕処理施設維持管理状況報告書</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
+      <c r="A2" s="39" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　破砕処理施設維持管理状況報告書"</f>
+        <v>令和9年度　破砕処理施設維持管理状況報告書</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="38"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="45"/>
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="49"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="54"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="49"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="50">
+      <c r="B7" s="33"/>
+      <c r="C7" s="55">
         <v>37070</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="42" t="s">
+      <c r="D7" s="53"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="43"/>
-      <c r="H7" s="34" t="s">
+      <c r="G7" s="33"/>
+      <c r="H7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="32" t="s">
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="33"/>
-      <c r="M7" s="34" t="s">
+      <c r="L7" s="31"/>
+      <c r="M7" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="33"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="31"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="39" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="34" t="s">
+      <c r="D8" s="47"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="44" t="s">
+      <c r="G8" s="31"/>
+      <c r="H8" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="51"/>
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
@@ -2388,8 +2374,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2431,7 +2417,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="35" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="16"/>
@@ -2450,7 +2436,7 @@
       <c r="O12" s="18"/>
     </row>
     <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="53"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="23"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -2467,7 +2453,7 @@
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="53"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="23"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2484,7 +2470,7 @@
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="53"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="23"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2501,7 +2487,7 @@
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="53"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="23"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -2518,7 +2504,7 @@
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="53"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="23"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -2535,7 +2521,7 @@
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="53"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="23"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2552,7 +2538,7 @@
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="53"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="23"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -2569,7 +2555,7 @@
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="53"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="23"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -2586,7 +2572,7 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="53"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="24"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2603,7 +2589,7 @@
       <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="53"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="21" t="s">
         <v>22</v>
       </c>
@@ -2622,7 +2608,7 @@
       <c r="O22" s="17"/>
     </row>
     <row r="23" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="54"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="22" t="s">
         <v>20</v>
       </c>
@@ -2665,7 +2651,7 @@
       <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -2737,7 +2723,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="53"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="28" t="s">
         <v>38</v>
       </c>
@@ -2807,7 +2793,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="53"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
@@ -2865,7 +2851,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="53"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="25" t="s">
         <v>39</v>
       </c>
@@ -2923,7 +2909,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="53"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="25" t="s">
         <v>40</v>
       </c>
@@ -2993,7 +2979,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="54"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
@@ -3051,7 +3037,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="35" t="s">
         <v>21</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -3072,7 +3058,7 @@
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="53"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="13" t="s">
         <v>25</v>
       </c>
@@ -3091,7 +3077,7 @@
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="53"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="15"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
@@ -3108,7 +3094,7 @@
       <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="54"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="10" t="s">
         <v>0</v>
       </c>
@@ -3145,8 +3131,8 @@
       <c r="O35" s="3"/>
     </row>
     <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="55"/>
-      <c r="B36" s="55"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -3162,8 +3148,8 @@
       <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="55"/>
-      <c r="B37" s="55"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="38"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -3179,7 +3165,7 @@
       <c r="O37" s="26"/>
     </row>
     <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="51"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="27"/>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -3196,7 +3182,7 @@
       <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="51"/>
+      <c r="A39" s="34"/>
       <c r="B39" s="27"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -3213,7 +3199,7 @@
       <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="51"/>
+      <c r="A40" s="34"/>
       <c r="B40" s="27"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
@@ -3264,14 +3250,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
@@ -3288,6 +3266,14 @@
     <mergeCell ref="C5:O5"/>
     <mergeCell ref="C6:O6"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/(枠)◯年度一式/管理月報/実施要領報告様式有価.xlsx
+++ b/(枠)◯年度一式/管理月報/実施要領報告様式有価.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90114859-F5D6-4323-8A4D-ECD4055FCECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB71D0F-275D-4DE5-A454-96AB79FF1B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="45" windowWidth="20535" windowHeight="15480" xr2:uid="{57CE4AD5-2BC3-4110-8DAF-C104A3A5DEF1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57CE4AD5-2BC3-4110-8DAF-C104A3A5DEF1}"/>
   </bookViews>
   <sheets>
     <sheet name="別記様式４" sheetId="7" r:id="rId1"/>
@@ -920,14 +920,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -935,6 +965,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
@@ -948,57 +999,6 @@
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2214,142 +2214,142 @@
       <c r="A1"/>
     </row>
     <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="39" t="str">
+      <c r="A2" s="29" t="str">
         <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度　破砕処理施設維持管理状況報告書"</f>
         <v>令和9年度　破砕処理施設維持管理状況報告書</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="45"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="38"/>
     </row>
     <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="52" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="49"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="49"/>
     </row>
     <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="55">
+      <c r="B7" s="43"/>
+      <c r="C7" s="50">
         <v>37070</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="32" t="s">
+      <c r="D7" s="48"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="29" t="s">
+      <c r="G7" s="43"/>
+      <c r="H7" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="42" t="s">
+      <c r="I7" s="35"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="29" t="s">
+      <c r="L7" s="33"/>
+      <c r="M7" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="30"/>
-      <c r="O7" s="31"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="33"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="46" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="29" t="s">
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="49" t="s">
+      <c r="G8" s="33"/>
+      <c r="H8" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="51"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
     </row>
     <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
@@ -2374,8 +2374,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="40"/>
-      <c r="B11" s="41"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2417,7 +2417,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="52" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="16"/>
@@ -2436,7 +2436,7 @@
       <c r="O12" s="18"/>
     </row>
     <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="36"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="23"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -2453,7 +2453,7 @@
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="36"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="23"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2470,7 +2470,7 @@
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="36"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="23"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2487,7 +2487,7 @@
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="36"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="23"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -2504,7 +2504,7 @@
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="36"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="23"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -2521,7 +2521,7 @@
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="36"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="23"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -2538,7 +2538,7 @@
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="36"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="23"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -2555,7 +2555,7 @@
       <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="36"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="23"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -2572,7 +2572,7 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="36"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="24"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2589,7 +2589,7 @@
       <c r="O21" s="12"/>
     </row>
     <row r="22" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="36"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="21" t="s">
         <v>22</v>
       </c>
@@ -2608,7 +2608,7 @@
       <c r="O22" s="17"/>
     </row>
     <row r="23" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="37"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="22" t="s">
         <v>20</v>
       </c>
@@ -2651,7 +2651,7 @@
       <c r="O23" s="12"/>
     </row>
     <row r="24" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="52" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -2723,7 +2723,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="36"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="28" t="s">
         <v>38</v>
       </c>
@@ -2793,7 +2793,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="36"/>
+      <c r="A26" s="53"/>
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
@@ -2851,7 +2851,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="36"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="25" t="s">
         <v>39</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="36"/>
+      <c r="A28" s="53"/>
       <c r="B28" s="25" t="s">
         <v>40</v>
       </c>
@@ -2979,7 +2979,7 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="37"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
@@ -3037,7 +3037,7 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="52" t="s">
         <v>21</v>
       </c>
       <c r="B30" s="11" t="s">
@@ -3058,7 +3058,7 @@
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="36"/>
+      <c r="A31" s="53"/>
       <c r="B31" s="13" t="s">
         <v>25</v>
       </c>
@@ -3077,7 +3077,7 @@
       <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="36"/>
+      <c r="A32" s="53"/>
       <c r="B32" s="15"/>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
@@ -3094,7 +3094,7 @@
       <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="37"/>
+      <c r="A33" s="54"/>
       <c r="B33" s="10" t="s">
         <v>0</v>
       </c>
@@ -3131,8 +3131,8 @@
       <c r="O35" s="3"/>
     </row>
     <row r="36" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="55"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -3148,8 +3148,8 @@
       <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="38"/>
-      <c r="B37" s="38"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="55"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
@@ -3165,7 +3165,7 @@
       <c r="O37" s="26"/>
     </row>
     <row r="38" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="34"/>
+      <c r="A38" s="51"/>
       <c r="B38" s="27"/>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -3182,7 +3182,7 @@
       <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="34"/>
+      <c r="A39" s="51"/>
       <c r="B39" s="27"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -3199,7 +3199,7 @@
       <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="34"/>
+      <c r="A40" s="51"/>
       <c r="B40" s="27"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
@@ -3250,6 +3250,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
@@ -3266,14 +3274,6 @@
     <mergeCell ref="C5:O5"/>
     <mergeCell ref="C6:O6"/>
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
